--- a/artfynd/A 13347-2024 artfynd.xlsx
+++ b/artfynd/A 13347-2024 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979930</v>
+        <v>130979907</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1428,7 +1428,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590789</v>
+        <v>591205</v>
       </c>
       <c r="R8" t="n">
-        <v>6963216</v>
+        <v>6963087</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979907</v>
+        <v>130979930</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1548,7 +1548,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591205</v>
+        <v>590789</v>
       </c>
       <c r="R9" t="n">
-        <v>6963087</v>
+        <v>6963216</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13347-2024 artfynd.xlsx
+++ b/artfynd/A 13347-2024 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979907</v>
+        <v>130979930</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1428,7 +1428,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591205</v>
+        <v>590789</v>
       </c>
       <c r="R8" t="n">
-        <v>6963087</v>
+        <v>6963216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979930</v>
+        <v>130979907</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1548,7 +1548,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590789</v>
+        <v>591205</v>
       </c>
       <c r="R9" t="n">
-        <v>6963216</v>
+        <v>6963087</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 13347-2024 artfynd.xlsx
+++ b/artfynd/A 13347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979906</v>
+        <v>130979917</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591163</v>
+        <v>591077</v>
       </c>
       <c r="R2" t="n">
-        <v>6963104</v>
+        <v>6963186</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,53 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979891</v>
+        <v>130979909</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590710</v>
+        <v>591185</v>
       </c>
       <c r="R3" t="n">
-        <v>6963217</v>
+        <v>6963058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979928</v>
+        <v>130979926</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590813</v>
+        <v>590852</v>
       </c>
       <c r="R4" t="n">
-        <v>6963212</v>
+        <v>6963248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,53 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979929</v>
+        <v>130979911</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590797</v>
+        <v>591152</v>
       </c>
       <c r="R5" t="n">
-        <v>6963219</v>
+        <v>6963132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979890</v>
+        <v>130979912</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,42 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590704</v>
+        <v>591115</v>
       </c>
       <c r="R6" t="n">
-        <v>6963217</v>
+        <v>6963152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979894</v>
+        <v>130979889</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590712</v>
+        <v>590701</v>
       </c>
       <c r="R7" t="n">
-        <v>6963209</v>
+        <v>6963240</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1298,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979907</v>
+        <v>130979890</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591205</v>
+        <v>590704</v>
       </c>
       <c r="R8" t="n">
-        <v>6963087</v>
+        <v>6963217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,7 +1408,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1418,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1515,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979930</v>
+        <v>130979891</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1483,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1558,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590789</v>
+        <v>590710</v>
       </c>
       <c r="R9" t="n">
-        <v>6963216</v>
+        <v>6963217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,12 +1538,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1573,7 @@
         <v>130979893</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,6 +1687,1926 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130979894</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590712</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6963209</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130979895</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6963193</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130979906</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591163</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6963104</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130979907</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>591205</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6963087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130979913</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591112</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6963159</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>möjligt bohål i asp 3.5 meter upp</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130979918</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>591073</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6963191</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130979919</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590971</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6963236</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130979920</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590960</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6963237</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130979921</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>590951</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6963242</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130979922</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>590936</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6963244</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130979923</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>590913</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6963246</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130979925</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>590855</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6963228</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130979927</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>590832</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6963235</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130979928</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>590813</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6963212</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130979929</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>590797</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6963219</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130979930</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>590789</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6963216</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13347-2024 artfynd.xlsx
+++ b/artfynd/A 13347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979926</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979912</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979889</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979890</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979893</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979894</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979895</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979906</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979907</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979913</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2407,6 +2482,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2527,6 +2607,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979919</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2647,6 +2732,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979920</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2767,6 +2857,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979921</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2887,6 +2982,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979922</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3007,6 +3107,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979923</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3127,6 +3232,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979925</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3247,6 +3357,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979927</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3367,6 +3482,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979928</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3487,6 +3607,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979929</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3607,8 +3732,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>